--- a/templates/template_input1.xlsx
+++ b/templates/template_input1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="안내" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="설정" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="인원" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="최소인력" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="설정" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="인원" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최소인력" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -691,11 +691,6 @@
           <t>공휴일</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-09-24, 2026-09-25, 2026-09-26</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">

--- a/templates/template_input1.xlsx
+++ b/templates/template_input1.xlsx
@@ -607,7 +607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -676,24 +676,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>리더8A운용</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>N</t>
+          <t>공휴일</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
-        <is>
-          <t>공휴일</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
         <is>
           <t>대체공휴일</t>
         </is>

--- a/templates/template_input1.xlsx
+++ b/templates/template_input1.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -485,7 +485,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>시트 구성 (3개, 전부 필수)</t>
+          <t>시트 구성 (① 설정 · ② 인원 · ③ 최소인력 3개는 필수, B팀은 선택)</t>
         </is>
       </c>
     </row>
@@ -580,17 +580,25 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr"/>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>선택: B팀(신입) — 이름 한 줄씩만. 근무 배정에는 전혀 관여하지 않고, 출력 근무표에
+'B' 구분란에 이름만 표시됩니다 — 파트장이 직접 배정하세요.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>이 파일만으로도 근무표 생성은 가능합니다</t>
-        </is>
-      </c>
+      <c r="A21" s="5" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>이 파일만으로도 근무표 생성은 가능합니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>신청(원티드)과 전월이월은 이 파일 안에 시트로 같이 넣을 수도 있지만, 화면의 입력②(전월 확정 근무표)와 입력③(원티드표)으로 따로 올리는 편이 관리하기 더 편합니다.</t>
         </is>
